--- a/pages/TEMPLATE WXREV.xlsx
+++ b/pages/TEMPLATE WXREV.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zavie\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{469A1D55-90E0-49C3-9018-5F81F206EDEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B420B37A-27A3-4B05-AD3B-F682D1C38D0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -585,8 +585,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="167" formatCode="0_);[Red]\(0\)"/>
-    <numFmt numFmtId="168" formatCode="00000"/>
+    <numFmt numFmtId="164" formatCode="0_);[Red]\(0\)"/>
+    <numFmt numFmtId="165" formatCode="00000"/>
   </numFmts>
   <fonts count="11">
     <font>
@@ -951,10 +951,10 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="justify"/>
     </xf>
-    <xf numFmtId="168" fontId="7" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="1" fontId="7" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -963,13 +963,13 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="justify"/>
     </xf>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="justify"/>
     </xf>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="justify"/>
     </xf>
-    <xf numFmtId="168" fontId="7" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="1" fontId="7" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -999,6 +999,13 @@
     <xf numFmtId="3" fontId="2" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1014,13 +1021,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1095,7 +1095,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
+      <xdr:colOff>276225</xdr:colOff>
       <xdr:row>46</xdr:row>
       <xdr:rowOff>28575</xdr:rowOff>
     </xdr:to>
@@ -1452,27 +1452,28 @@
     <col min="2" max="2" width="7.28515625" customWidth="1"/>
     <col min="3" max="3" width="8.85546875" customWidth="1"/>
     <col min="4" max="4" width="8.5703125" customWidth="1"/>
-    <col min="5" max="5" width="10" customWidth="1"/>
-    <col min="7" max="7" width="9.85546875" customWidth="1"/>
-    <col min="8" max="8" width="11" customWidth="1"/>
+    <col min="5" max="5" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.140625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="8.7109375" customWidth="1"/>
     <col min="10" max="10" width="8.85546875" customWidth="1"/>
-    <col min="11" max="11" width="14.7109375" customWidth="1"/>
+    <col min="11" max="11" width="12.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:11" ht="15.75">
-      <c r="B1" s="29" t="s">
+      <c r="B1" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
-      <c r="F1" s="29"/>
-      <c r="G1" s="29"/>
-      <c r="H1" s="29"/>
-      <c r="I1" s="29"/>
-      <c r="J1" s="29"/>
-      <c r="K1" s="29"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
+      <c r="H1" s="32"/>
+      <c r="I1" s="32"/>
+      <c r="J1" s="32"/>
+      <c r="K1" s="32"/>
     </row>
     <row r="2" spans="2:11">
       <c r="B2" s="1"/>
@@ -1487,32 +1488,32 @@
       <c r="K2" s="1"/>
     </row>
     <row r="3" spans="2:11" ht="15.75">
-      <c r="B3" s="30" t="s">
+      <c r="B3" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="30"/>
-      <c r="D3" s="30"/>
-      <c r="E3" s="30"/>
-      <c r="F3" s="30"/>
-      <c r="G3" s="30"/>
-      <c r="H3" s="30"/>
-      <c r="I3" s="30"/>
-      <c r="J3" s="30"/>
-      <c r="K3" s="30"/>
+      <c r="C3" s="33"/>
+      <c r="D3" s="33"/>
+      <c r="E3" s="33"/>
+      <c r="F3" s="33"/>
+      <c r="G3" s="33"/>
+      <c r="H3" s="33"/>
+      <c r="I3" s="33"/>
+      <c r="J3" s="33"/>
+      <c r="K3" s="33"/>
     </row>
     <row r="4" spans="2:11" ht="15.75">
-      <c r="B4" s="36"/>
-      <c r="C4" s="36"/>
-      <c r="D4" s="36"/>
-      <c r="E4" s="36" t="s">
+      <c r="B4" s="29"/>
+      <c r="C4" s="29"/>
+      <c r="D4" s="29"/>
+      <c r="E4" s="29"/>
+      <c r="F4" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="F4" s="36"/>
-      <c r="G4" s="36"/>
-      <c r="H4" s="36"/>
-      <c r="I4" s="36"/>
-      <c r="J4" s="36"/>
-      <c r="K4" s="36"/>
+      <c r="G4" s="29"/>
+      <c r="H4" s="29"/>
+      <c r="I4" s="29"/>
+      <c r="J4" s="29"/>
+      <c r="K4" s="29"/>
     </row>
     <row r="5" spans="2:11">
       <c r="B5" s="2"/>
@@ -1548,10 +1549,10 @@
       <c r="H6" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="I6" s="31" t="s">
+      <c r="I6" s="34" t="s">
         <v>10</v>
       </c>
-      <c r="J6" s="32"/>
+      <c r="J6" s="35"/>
       <c r="K6" s="23" t="s">
         <v>11</v>
       </c>
@@ -1578,10 +1579,10 @@
       <c r="H7" s="12">
         <v>7</v>
       </c>
-      <c r="I7" s="33">
+      <c r="I7" s="36">
         <v>8</v>
       </c>
-      <c r="J7" s="33"/>
+      <c r="J7" s="36"/>
       <c r="K7" s="24">
         <v>9</v>
       </c>
@@ -2021,20 +2022,20 @@
       <c r="K38" s="28"/>
     </row>
     <row r="40" spans="2:11">
-      <c r="B40" s="34" t="s">
+      <c r="B40" s="31" t="s">
         <v>43</v>
       </c>
-      <c r="C40" s="34"/>
-      <c r="D40" s="34"/>
-      <c r="E40" s="34"/>
-      <c r="F40" s="34"/>
+      <c r="C40" s="31"/>
+      <c r="D40" s="31"/>
+      <c r="E40" s="31"/>
+      <c r="F40" s="31"/>
       <c r="G40" s="1"/>
-      <c r="H40" s="34" t="s">
+      <c r="H40" s="31" t="s">
         <v>44</v>
       </c>
-      <c r="I40" s="34"/>
-      <c r="J40" s="34"/>
-      <c r="K40" s="34"/>
+      <c r="I40" s="31"/>
+      <c r="J40" s="31"/>
+      <c r="K40" s="31"/>
     </row>
     <row r="41" spans="2:11">
       <c r="B41" s="21"/>
@@ -2049,34 +2050,34 @@
       <c r="K41" s="21"/>
     </row>
     <row r="42" spans="2:11">
-      <c r="B42" s="34" t="s">
+      <c r="B42" s="31" t="s">
         <v>45</v>
       </c>
-      <c r="C42" s="34"/>
-      <c r="D42" s="34"/>
-      <c r="E42" s="34"/>
-      <c r="F42" s="34"/>
+      <c r="C42" s="31"/>
+      <c r="D42" s="31"/>
+      <c r="E42" s="31"/>
+      <c r="F42" s="31"/>
       <c r="G42" s="1"/>
-      <c r="H42" s="34" t="s">
+      <c r="H42" s="31" t="s">
         <v>46</v>
       </c>
-      <c r="I42" s="34"/>
-      <c r="J42" s="34"/>
-      <c r="K42" s="34"/>
+      <c r="I42" s="31"/>
+      <c r="J42" s="31"/>
+      <c r="K42" s="31"/>
     </row>
     <row r="43" spans="2:11">
-      <c r="B43" s="34" t="s">
+      <c r="B43" s="31" t="s">
         <v>47</v>
       </c>
-      <c r="C43" s="34"/>
-      <c r="D43" s="34"/>
-      <c r="E43" s="34"/>
-      <c r="F43" s="34"/>
+      <c r="C43" s="31"/>
+      <c r="D43" s="31"/>
+      <c r="E43" s="31"/>
+      <c r="F43" s="31"/>
       <c r="G43" s="1"/>
-      <c r="H43" s="34"/>
-      <c r="I43" s="34"/>
-      <c r="J43" s="34"/>
-      <c r="K43" s="34"/>
+      <c r="H43" s="31"/>
+      <c r="I43" s="31"/>
+      <c r="J43" s="31"/>
+      <c r="K43" s="31"/>
     </row>
     <row r="44" spans="2:11">
       <c r="B44" s="21"/>
@@ -2115,39 +2116,43 @@
       <c r="K46" s="21"/>
     </row>
     <row r="47" spans="2:11">
-      <c r="B47" s="35" t="s">
+      <c r="B47" s="30" t="s">
         <v>48</v>
       </c>
-      <c r="C47" s="35"/>
-      <c r="D47" s="35"/>
-      <c r="E47" s="35"/>
-      <c r="F47" s="35"/>
+      <c r="C47" s="30"/>
+      <c r="D47" s="30"/>
+      <c r="E47" s="30"/>
+      <c r="F47" s="30"/>
       <c r="G47" s="1"/>
-      <c r="H47" s="35" t="s">
+      <c r="H47" s="30" t="s">
         <v>49</v>
       </c>
-      <c r="I47" s="35"/>
-      <c r="J47" s="35"/>
-      <c r="K47" s="35"/>
+      <c r="I47" s="30"/>
+      <c r="J47" s="30"/>
+      <c r="K47" s="30"/>
     </row>
     <row r="48" spans="2:11">
-      <c r="B48" s="34" t="s">
+      <c r="B48" s="31" t="s">
         <v>50</v>
       </c>
-      <c r="C48" s="34"/>
-      <c r="D48" s="34"/>
-      <c r="E48" s="34"/>
-      <c r="F48" s="34"/>
+      <c r="C48" s="31"/>
+      <c r="D48" s="31"/>
+      <c r="E48" s="31"/>
+      <c r="F48" s="31"/>
       <c r="G48" s="1"/>
-      <c r="H48" s="34" t="s">
+      <c r="H48" s="31" t="s">
         <v>51</v>
       </c>
-      <c r="I48" s="34"/>
-      <c r="J48" s="34"/>
-      <c r="K48" s="34"/>
+      <c r="I48" s="31"/>
+      <c r="J48" s="31"/>
+      <c r="K48" s="31"/>
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="B1:K1"/>
+    <mergeCell ref="B3:K3"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="I7:J7"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="H47:K47"/>
     <mergeCell ref="B48:F48"/>
@@ -2158,10 +2163,6 @@
     <mergeCell ref="H42:K42"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="H43:K43"/>
-    <mergeCell ref="B1:K1"/>
-    <mergeCell ref="B3:K3"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="I7:J7"/>
   </mergeCells>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup scale="96" orientation="portrait" r:id="rId1"/>
